--- a/banks/W13_Kahoot匯入.xlsx
+++ b/banks/W13_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,30 +491,30 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>投資期</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>糖解作用</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>收穫期</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>肝醣分解</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>投資期</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>收穫期</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>糖解作用</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -526,30 +526,30 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>丙酮酸</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>丙酮酸激酶</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>醣質新生</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>己糖激酶</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>丙酮酸激酶</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>醣質新生</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>丙酮酸</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -561,30 +561,30 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>肝醣分解</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>醣質新生</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>磷酸果糖激酶</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>肝醣分解</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>己糖激酶</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>醣質新生</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -601,25 +601,25 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>肝醣分解</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>丙酮酸激酶</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>磷酸果糖激酶</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>肝醣分解</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -631,30 +631,30 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>丙酮酸</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>肝醣分解</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>醣質新生</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>糖解作用</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>丙酮酸</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>肝醣分解</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>醣質新生</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -666,30 +666,30 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
+          <t>投資期</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>醣質新生</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>發酵</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>收穫期</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>投資期</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>醣質新生</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -706,25 +706,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>乙醇</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>收穫期</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>醣質新生</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>乙醇</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -736,19 +736,19 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
+          <t>糖解作用</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>己糖激酶</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>受質層次磷酸化</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>糖解作用</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>磷酸果糖激酶</t>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>乙醇</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>乳酸</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>投資期</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>收穫期</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>乙醇</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>乳酸</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -841,19 +841,19 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
+          <t>收穫期</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>乙醇</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>乳酸</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>收穫期</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>乙醇</t>
-        </is>
-      </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
           <t>肝醣分解</t>
@@ -864,7 +864,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -881,17 +881,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>肝醣分解</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>糖解作用</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>丙酮酸</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>肝醣分解</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -911,22 +911,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>糖解作用</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>收穫期</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>肝醣分解</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>丙酮酸激酶</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>糖解作用</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>肝醣分解</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>收穫期</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>肝醣分解</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>受質層次磷酸化</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>肝醣分解</t>
-        </is>
-      </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>醣質新生</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>戊糖磷酸途徑</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>醣質新生</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -981,28 +981,168 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
+          <t>戊糖磷酸途徑</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>醣質新生</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>己糖激酶</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>菸鹼醯胺腺嘌呤二核苷酸</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:糖解作用) 標號1是什麼?</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>投資期</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>醣質新生</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>己糖激酶</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>收穫期</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>發酵</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:糖解作用) 標號2是什麼?</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>肝醣分解</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>收穫期</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>投資期</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>戊糖磷酸途徑</t>
         </is>
       </c>
-      <c r="F16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>丙酮酸激酶—糖解第一步</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>己糖激酶—磷酸化葡萄糖</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>乳酸去氫酶—醣質新生酶</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>磷酸果糖激酶—收穫期關鍵酶</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>1分子葡萄糖經糖解作用，淨產生多少ATP與NADH?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>2 ATP、2 NADH</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2 ATP、4 NADH</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>4 ATP、2 NADH</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4 ATP、4 NADH</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
